--- a/data.mn/public/datasets/gdp-growth-rate.xlsx
+++ b/data.mn/public/datasets/gdp-growth-rate.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="English" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Монгол" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -723,4 +724,322 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B37"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>он</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>утга</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1990</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-3.76</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1991</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-8.699999999999999</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1992</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-9.300000000000001</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1993</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-3.2</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1994</v>
+      </c>
+      <c r="B6" t="n">
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1995</v>
+      </c>
+      <c r="B7" t="n">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>1996</v>
+      </c>
+      <c r="B8" t="n">
+        <v>2.2</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>1997</v>
+      </c>
+      <c r="B9" t="n">
+        <v>3.9</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>1998</v>
+      </c>
+      <c r="B10" t="n">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>1999</v>
+      </c>
+      <c r="B11" t="n">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>2000</v>
+      </c>
+      <c r="B12" t="n">
+        <v>1.1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>2001</v>
+      </c>
+      <c r="B13" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>2002</v>
+      </c>
+      <c r="B14" t="n">
+        <v>4.7</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>2003</v>
+      </c>
+      <c r="B15" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>2004</v>
+      </c>
+      <c r="B16" t="n">
+        <v>10.6</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>2005</v>
+      </c>
+      <c r="B17" t="n">
+        <v>7.3</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>2006</v>
+      </c>
+      <c r="B18" t="n">
+        <v>8.6</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>2007</v>
+      </c>
+      <c r="B19" t="n">
+        <v>10.2</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>2008</v>
+      </c>
+      <c r="B20" t="n">
+        <v>8.9</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>2009</v>
+      </c>
+      <c r="B21" t="n">
+        <v>-1.3</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>2010</v>
+      </c>
+      <c r="B22" t="n">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>2011</v>
+      </c>
+      <c r="B23" t="n">
+        <v>17.3</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>2012</v>
+      </c>
+      <c r="B24" t="n">
+        <v>12.3</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>2013</v>
+      </c>
+      <c r="B25" t="n">
+        <v>11.6</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>2014</v>
+      </c>
+      <c r="B26" t="n">
+        <v>7.9</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>2015</v>
+      </c>
+      <c r="B27" t="n">
+        <v>2.38</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>2016</v>
+      </c>
+      <c r="B28" t="n">
+        <v>1.49</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>2017</v>
+      </c>
+      <c r="B29" t="n">
+        <v>5.64</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>2018</v>
+      </c>
+      <c r="B30" t="n">
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>2019</v>
+      </c>
+      <c r="B31" t="n">
+        <v>5.6</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B32" t="n">
+        <v>-4.6</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B33" t="n">
+        <v>1.64</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B34" t="n">
+        <v>5.03</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B35" t="n">
+        <v>7.42</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B36" t="n">
+        <v>5.12</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B37" t="n">
+        <v>6.84</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>